--- a/outputs/sample_candidate_ranking.xlsx
+++ b/outputs/sample_candidate_ranking.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Candidate Ranking'!$A$1:$W$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Detailed Evaluation'!$A$1:$H$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Candidate Ranking'!$A$1:$W$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Detailed Evaluation'!$A$1:$H$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -567,7 +567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W9"/>
+  <dimension ref="A1:W10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -822,58 +822,166 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Candidate 007</t>
+          <t>Priya Raghavan</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>scanned_resume.pdf</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Partial Match</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>6 years (stated in resume) · Most recent relevant title: Performance Marketing Lead · BrightPath Learning, Vertex Retail</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>20.7/25</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>10.4/20</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>0/10</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>7.3/10</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>3.8/10</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>• Meets the JD minimum of 5 years with 6 years (stated in resume).
+• Mandatory: strong command of conversion rate optimization and A/B testing. — 100% relevance. Evidence: "Ran continuous A/B testing on landing pages and ad creatives."
+• Required: proven expertise running Google Ads and Meta Ads at scale. — 89% relevance. Evidence: "Owned paid acquisition across Google Ads and Meta Ads with a monthly budget of INR 90 lakh."
+• Own and scale paid acquisition across Google Ads and Meta Ads with a monthly budget above INR 1 crore. — 85% relevance. Evidence: "Owned paid acquisition across Google Ads and Meta Ads with a monthly budget of INR 90 lakh."
+• This is a hybrid role based in Bengaluru. Candidates must be willing to work from the Bengaluru office thre... — 85% relevance. Evidence: "Location: Bengaluru"
+• Essential: working knowledge of GA4 and marketing analytics dashboards. — 80% relevance. Evidence: "Reported CAC and ROAS to leadership weekly using GA4."</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>• Preferred requirements not evidenced: Partner with the content team on ad copy and landing page messaging for high-consideration programs.; Manage and mentor a team of two performance marketing executives.; Preferred: experience in edtech or another high-...</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>Not mentioned in resume</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>• Notice period: Not mentioned in resume</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>Not Reviewed</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr"/>
+      <c r="V3" s="3" t="inlineStr"/>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Candidate 008</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
           <t>unnamed_candidate_resume.docx</t>
         </is>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D4" s="4" t="n">
         <v>54.2</v>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Partial Match</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>8 years (stated in resume) · Most recent relevant title: Growth Marketing Lead</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>20.9/25</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>7.4/20</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>0/10</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>8.1/10</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>3.5/10</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>• This is a hybrid role based in Bengaluru. Candidates must be willing to work from the Bengaluru office three days a week.</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>• Meets the JD minimum of 5 years with 8 years (stated in resume).
 • Mandatory: strong command of conversion rate optimization and A/B testing. — 100% relevance. Evidence: "Led conversion rate optimization and a continuous A/B testing programme on landing pages."
@@ -883,26 +991,26 @@
 • Essential: working knowledge of GA4 and marketing analytics dashboards. — 84% relevance. Evidence: "Used GA4 and SQL for funnel analysis and cohort reporting."</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>• Mandatory requirement not met — This is a hybrid role based in Bengaluru. Candidates must be willing to work from the Bengaluru office thre...: no supporting evidence in the resume.
 • Preferred requirements not evidenced: Drive down cost per enrolment while growing qualified lead volume quarter on quarter.; Build and run a structured experimentation roadmap across creatives, landing pages and audiences.; Partner with the content team o...</t>
         </is>
       </c>
-      <c r="O3" s="3" t="n">
+      <c r="O4" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="P3" s="3" t="inlineStr">
+      <c r="P4" s="3" t="inlineStr">
         <is>
           <t>Not mentioned in resume</t>
         </is>
       </c>
-      <c r="Q3" s="3" t="inlineStr">
+      <c r="Q4" s="3" t="inlineStr">
         <is>
           <t>Not mentioned in resume</t>
         </is>
       </c>
-      <c r="R3" s="3" t="inlineStr">
+      <c r="R4" s="3" t="inlineStr">
         <is>
           <t>• Current location (the JD states a location requirement): Not mentioned in resume
 • Notice period: Not mentioned in resume
@@ -910,84 +1018,84 @@
 • No resume content addressing: This is a hybrid role based in Bengaluru. Candidates must be willing to work from the Bengaluru office three days a w...</t>
         </is>
       </c>
-      <c r="S3" s="3" t="inlineStr">
+      <c r="S4" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="T3" s="3" t="inlineStr">
+      <c r="T4" s="3" t="inlineStr">
         <is>
           <t>Not Reviewed</t>
         </is>
       </c>
-      <c r="U3" s="3" t="inlineStr"/>
-      <c r="V3" s="3" t="inlineStr"/>
-      <c r="W3" s="3" t="inlineStr">
+      <c r="U4" s="3" t="inlineStr"/>
+      <c r="V4" s="3" t="inlineStr"/>
+      <c r="W4" s="3" t="inlineStr">
         <is>
           <t>processed</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Rahul Nair</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>rahul_nair_resume.docx</t>
         </is>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D5" s="4" t="n">
         <v>30.7</v>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>Weak Match</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>4 years (stated in resume) · Most recent relevant title: Digital Marketing Specialist · CloudLedger Systems, Brightforms</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>11.9/25</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>3.2/20</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>0/10</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>7.3/10</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>1.6/10</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>• Required: proven expertise running Google Ads and Meta Ads at scale.
 • Mandatory: strong command of conversion rate optimization and A/B testing.
 • This is a hybrid role based in Bengaluru. Candidates must be willing to work from the Bengaluru office three days a week.</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>• Nice to have: exposure to lifecycle and email marketing. — 80% relevance. Evidence: "Supported SEO and email marketing campaigns."
 • Advantage: Google Ads certification. — 80% relevance. Evidence: "Grew inbound demo requests 60% year on year through paid search and content."
@@ -996,7 +1104,7 @@
 • Must have experience owning CAC, ROAS and unit economics for a paid funnel. — 67% relevance. Evidence: "Built monthly reporting on pipeline contribution and cost per lead."</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>• Mandatory requirement not met — Required: proven expertise running Google Ads and Meta Ads at scale.: no supporting evidence in the resume.
 • Mandatory requirement not met — Mandatory: strong command of conversion rate optimization and A/B testing.: no supporting evidence in the resume.
@@ -1005,96 +1113,96 @@
 • Preferred requirements not evidenced: Own and scale paid acquisition across Google Ads and Meta Ads with a monthly budget above INR 1 crore.; Drive down cost per enrolment while growing qualified lead volume quarter on quarter.; Build and run a structured...</t>
         </is>
       </c>
-      <c r="O4" s="3" t="n">
+      <c r="O5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="P4" s="3" t="inlineStr">
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>Pune</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="inlineStr">
+      <c r="Q5" s="3" t="inlineStr">
         <is>
           <t>60 days</t>
         </is>
       </c>
-      <c r="R4" s="3" t="inlineStr">
+      <c r="R5" s="3" t="inlineStr">
         <is>
           <t>• No resume content addressing: Required: proven expertise running Google Ads and Meta Ads at scale.
 • No resume content addressing: Mandatory: strong command of conversion rate optimization and A/B testing.</t>
         </is>
       </c>
-      <c r="S4" s="3" t="inlineStr">
+      <c r="S5" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="T4" s="3" t="inlineStr">
+      <c r="T5" s="3" t="inlineStr">
         <is>
           <t>Not Reviewed</t>
         </is>
       </c>
-      <c r="U4" s="3" t="inlineStr"/>
-      <c r="V4" s="3" t="inlineStr"/>
-      <c r="W4" s="3" t="inlineStr">
+      <c r="U5" s="3" t="inlineStr"/>
+      <c r="V5" s="3" t="inlineStr"/>
+      <c r="W5" s="3" t="inlineStr">
         <is>
           <t>processed</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Vikram Desai</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>vikram_desai_resume.pdf</t>
         </is>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D6" s="4" t="n">
         <v>11.7</v>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Weak Match</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>6 years (stated in resume) · Most recent relevant title: Senior Software Engineer · Nimbus Data Systems, Trailhead Tech</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>0/25</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>0.8/20</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>0/10</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>3.3/10</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>0.5/10</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>• Must have 5+ years of hands-on performance marketing experience.
 • Required: proven expertise running Google Ads and Meta Ads at scale.
@@ -1104,13 +1212,13 @@
 • This is a hybrid role based in Bengaluru. Candidates must be willing to work from the Bengaluru office three days a week.</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>• Meets the JD minimum of 5 years with 6 years (stated in resume).
 • Required qualification: Bachelor's degree in any discipline. — 67% relevance. Evidence: "B.Tech, Information Technology - NIT Warangal, 2018"</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t>• Mandatory requirement not met — Must have 5+ years of hands-on performance marketing experience.: no supporting evidence in the resume.
 • Mandatory requirement not met — Required: proven expertise running Google Ads and Meta Ads at scale.: no supporting evidence in the resume.
@@ -1120,20 +1228,20 @@
 • Preferred requirements not evidenced: Own and scale paid acquisition across Google Ads and Meta Ads with a monthly budget above INR 1 crore.; Drive down cost per enrolment while growing qualified lead volume quarter on quarter.; Build and run a structured...</t>
         </is>
       </c>
-      <c r="O5" s="3" t="n">
+      <c r="O6" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="P5" s="3" t="inlineStr">
+      <c r="P6" s="3" t="inlineStr">
         <is>
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="Q5" s="3" t="inlineStr">
+      <c r="Q6" s="3" t="inlineStr">
         <is>
           <t>Not mentioned in resume</t>
         </is>
       </c>
-      <c r="R5" s="3" t="inlineStr">
+      <c r="R6" s="3" t="inlineStr">
         <is>
           <t>• Notice period: Not mentioned in resume
 • No resume content addressing: Must have 5+ years of hands-on performance marketing experience.
@@ -1143,110 +1251,21 @@
 • No resume content addressing: Must have experience owning CAC, ROAS and unit economics for a paid funnel.</t>
         </is>
       </c>
-      <c r="S5" s="3" t="inlineStr">
+      <c r="S6" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="T5" s="3" t="inlineStr">
+      <c r="T6" s="3" t="inlineStr">
         <is>
           <t>Not Reviewed</t>
         </is>
       </c>
-      <c r="U5" s="3" t="inlineStr"/>
-      <c r="V5" s="3" t="inlineStr"/>
-      <c r="W5" s="3" t="inlineStr">
+      <c r="U6" s="3" t="inlineStr"/>
+      <c r="V6" s="3" t="inlineStr"/>
+      <c r="W6" s="3" t="inlineStr">
         <is>
           <t>processed</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr"/>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>Anjali Mehta</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>anjali_mehta_resume_copy.docx</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr"/>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>Insufficient Information</t>
-        </is>
-      </c>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>Not mentioned in resume</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J6" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K6" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" s="9" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="M6" s="9" t="inlineStr"/>
-      <c r="N6" s="9" t="inlineStr"/>
-      <c r="O6" s="9" t="inlineStr">
-        <is>
-          <t>Not mentioned in resume</t>
-        </is>
-      </c>
-      <c r="P6" s="9" t="inlineStr">
-        <is>
-          <t>Not mentioned in resume</t>
-        </is>
-      </c>
-      <c r="Q6" s="9" t="inlineStr">
-        <is>
-          <t>Not mentioned in resume</t>
-        </is>
-      </c>
-      <c r="R6" s="9" t="inlineStr"/>
-      <c r="S6" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T6" s="9" t="inlineStr">
-        <is>
-          <t>Not Reviewed</t>
-        </is>
-      </c>
-      <c r="U6" s="9" t="inlineStr"/>
-      <c r="V6" s="9" t="inlineStr"/>
-      <c r="W6" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">duplicate: </t>
         </is>
       </c>
     </row>
@@ -1254,12 +1273,12 @@
       <c r="A7" s="8" t="inlineStr"/>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Candidate 003</t>
+          <t>Anjali Mehta</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>corrupted_resume.pdf</t>
+          <t>anjali_mehta_resume_copy.docx</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr"/>
@@ -1335,7 +1354,7 @@
       <c r="V7" s="9" t="inlineStr"/>
       <c r="W7" s="9" t="inlineStr">
         <is>
-          <t>failed: Corrupted or unreadable PDF (No /Root object! - Is this really a PDF?).</t>
+          <t xml:space="preserve">duplicate: </t>
         </is>
       </c>
     </row>
@@ -1343,12 +1362,12 @@
       <c r="A8" s="8" t="inlineStr"/>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Candidate 004</t>
+          <t>Candidate 003</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>empty_resume.txt</t>
+          <t>corrupted_resume.pdf</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr"/>
@@ -1424,7 +1443,7 @@
       <c r="V8" s="9" t="inlineStr"/>
       <c r="W8" s="9" t="inlineStr">
         <is>
-          <t>failed: Empty file (0 bytes).</t>
+          <t>failed: Corrupted or unreadable PDF (No /Root object! - Is this really a PDF?).</t>
         </is>
       </c>
     </row>
@@ -1432,12 +1451,12 @@
       <c r="A9" s="8" t="inlineStr"/>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Candidate 005</t>
+          <t>Candidate 004</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>meera_iyer_resume.txt</t>
+          <t>empty_resume.txt</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr"/>
@@ -1513,13 +1532,102 @@
       <c r="V9" s="9" t="inlineStr"/>
       <c r="W9" s="9" t="inlineStr">
         <is>
+          <t>failed: Empty file (0 bytes).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr"/>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Candidate 005</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>meera_iyer_resume.txt</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr"/>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>Insufficient Information</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>Not mentioned in resume</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L10" s="9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M10" s="9" t="inlineStr"/>
+      <c r="N10" s="9" t="inlineStr"/>
+      <c r="O10" s="9" t="inlineStr">
+        <is>
+          <t>Not mentioned in resume</t>
+        </is>
+      </c>
+      <c r="P10" s="9" t="inlineStr">
+        <is>
+          <t>Not mentioned in resume</t>
+        </is>
+      </c>
+      <c r="Q10" s="9" t="inlineStr">
+        <is>
+          <t>Not mentioned in resume</t>
+        </is>
+      </c>
+      <c r="R10" s="9" t="inlineStr"/>
+      <c r="S10" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T10" s="9" t="inlineStr">
+        <is>
+          <t>Not Reviewed</t>
+        </is>
+      </c>
+      <c r="U10" s="9" t="inlineStr"/>
+      <c r="V10" s="9" t="inlineStr"/>
+      <c r="W10" s="9" t="inlineStr">
+        <is>
           <t>failed: Empty resume — no usable text could be extracted.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W9"/>
-  <conditionalFormatting sqref="D2:D9">
+  <autoFilter ref="A1:W10"/>
+  <conditionalFormatting sqref="D2:D10">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -1531,7 +1639,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L9">
+  <conditionalFormatting sqref="L2:L10">
     <cfRule type="cellIs" priority="2" operator="notEqual" dxfId="0">
       <formula>"None"</formula>
     </cfRule>
@@ -1546,7 +1654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1671,7 +1779,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>• "Performance marketer with 7 years of experience scaling paid acquisition for"
+          <t>• "Performance marketer with 7 years of experience scaling paid acquisition for subscription and high-consideration consumer products."
 • "Ran AdWords search, shopping and paid social campaigns for a D2C marketplace."
 • "Ran structured A/B testing on landing pages, lifting checkout conversion rate from 3.1% to 5.4%."</t>
         </is>
@@ -1877,12 +1985,12 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Candidate 007</t>
+          <t>Priya Raghavan</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>unnamed_candidate_resume.docx</t>
+          <t>scanned_resume.pdf</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -1891,205 +1999,478 @@
         </is>
       </c>
       <c r="D9" s="12" t="n">
-        <v>14.3</v>
+        <v>16.8</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>25</v>
       </c>
       <c r="F9" s="13" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Role relevance 52%, title relevance 67%, duration fit 100%. Most relevant title held: Performance Marketing Lead 6 years of experience (stated in resume) meets the JD minimum of 5.</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>• "Owned paid acquisition across Google Ads and Meta Ads with a monthly budget of INR 90 lakh."
+• "Performance marketing lead with 6 years of experience scaling paid acquisition for consumer subscription products."
+• "Reduced cost per enrolment by 28% while growing qualified leads 1.9x."</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Priya Raghavan</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>scanned_resume.pdf</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Required Skills</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="F10" s="13" t="n">
+        <v>0.828</v>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Evidenced 5 of 5 required skill/experience requirement(s). All required items are supported by resume evidence.</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>• "Performance marketing lead with 6 years of experience scaling paid acquisition for consumer subscription products."
+• "Owned paid acquisition across Google Ads and Meta Ads with a monthly budget of INR 90 lakh."
+• "Ran continuous A/B testing on landing pages and ad creatives."</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Priya Raghavan</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>scanned_resume.pdf</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>JD Alignment</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Overall requirement coverage 55%; evidence aligns with 4 of 6 key responsibilities in the JD.</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>• "Owned paid acquisition across Google Ads and Meta Ads with a monthly budget of INR 90 lakh."
+• "Reduced cost per enrolment by 28% while growing qualified leads 1.9x."
+• "Ran continuous A/B testing on landing pages and ad creatives."</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Priya Raghavan</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>scanned_resume.pdf</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Industry / Domain Relevance</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>No resume evidence of the industry/domain the JD asks for: Preferred: experience in edtech or another high-consideration B2C c....</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>No direct quote available for this category.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Priya Raghavan</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>scanned_resume.pdf</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Education &amp; Certifications</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" s="13" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Matched 2 of 2 education/certification requirement(s).</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>• "B.Sc Statistics - Bangalore University, 2016"
+• "Ran paid search campaigns for an ecommerce marketplace."</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Priya Raghavan</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>scanned_resume.pdf</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Preferred Requirements</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E14" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" s="13" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Evidenced 5 of 11 preferred requirement(s).</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>• "Owned paid acquisition across Google Ads and Meta Ads with a monthly budget of INR 90 lakh."
+• "Reduced cost per enrolment by 28% while growing qualified leads 1.9x."
+• "Ran continuous A/B testing on landing pages and ad creatives."</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>Priya Raghavan</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>scanned_resume.pdf</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>Mandatory Requirements</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="E15" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="F15" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>Met: • Must have 5+ years of hands-on performance marketing experience.
+• Required: proven expertise running Google Ads and Meta Ads at scale.
+• Mandatory: strong command of conversion rate optimization and A/B testing.
+• Essential: working knowledge of GA4 and marketing analytics dashboards.
+• Required qualification: Bachelor's degree in any discipline.
+• Must have experience owning CAC, ROAS and unit economics for a paid funnel.
+• This is a hybrid role based in Bengaluru. Candidates must be willing to work from the Bengaluru office three days a week.
+Missed: None</t>
+        </is>
+      </c>
+      <c r="H15" s="14" t="inlineStr">
+        <is>
+          <t>• "[Mandatory: strong command of conversion rate optimization...] Ran continuous A/B testing on landing pages and ad creatives."
+• "[Required: proven expertise running Google Ads and Meta Ad...] Owned paid acquisition across Google Ads and Meta Ads with a monthly budget of INR 90 lakh."
+• "[This is a hybrid role based in Bengaluru. Candidates must...] Location: Bengaluru"
+• "[Essential: working knowledge of GA4 and marketing analyti...] Reported CAC and ROAS to leadership weekly using GA4."
+• "[Advantage: Google Ads certification.] Ran paid search campaigns for an ecommerce marketplace."
+• "[Must have 5+ years of hands-on performance marketing expe...] Performance marketing lead with 6 years of experience scaling paid acquisition for consumer subscription products."</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Candidate 008</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>unnamed_candidate_resume.docx</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Relevant Experience</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="F16" s="13" t="n">
         <v>0.5720000000000001</v>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>Role relevance 28%, title relevance 83%, duration fit 100%. Most relevant title held: Performance Marketing Manager 8 years of experience (stated in resume) meets the JD minimum of 5.</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>• "Growth marketing lead with 8 years of experience in paid acquisition for"
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>• "Growth marketing lead with 8 years of experience in paid acquisition for consumer subscription businesses."
 • "Owned paid media across Google Ads, Meta Ads and programmatic display."
 • "Led conversion rate optimization and a continuous A/B testing programme on landing pages."</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Candidate 007</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Candidate 008</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>unnamed_candidate_resume.docx</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Required Skills</t>
         </is>
       </c>
-      <c r="D10" s="12" t="n">
+      <c r="D17" s="12" t="n">
         <v>20.9</v>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="E17" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="F10" s="13" t="n">
+      <c r="F17" s="13" t="n">
         <v>0.836</v>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>Evidenced 5 of 5 required skill/experience requirement(s). All required items are supported by resume evidence.</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>• "Growth marketing lead with 8 years of experience in paid acquisition for"
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>• "Growth marketing lead with 8 years of experience in paid acquisition for consumer subscription businesses."
 • "Owned paid media across Google Ads, Meta Ads and programmatic display."
 • "Led conversion rate optimization and a continuous A/B testing programme on landing pages."</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Candidate 007</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Candidate 008</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>unnamed_candidate_resume.docx</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>JD Alignment</t>
         </is>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="D18" s="12" t="n">
         <v>7.4</v>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="E18" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="F11" s="13" t="n">
+      <c r="F18" s="13" t="n">
         <v>0.37</v>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>Overall requirement coverage 48%; evidence aligns with 1 of 6 key responsibilities in the JD.</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>• "Owned paid media across Google Ads, Meta Ads and programmatic display."</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Candidate 007</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Candidate 008</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>unnamed_candidate_resume.docx</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Industry / Domain Relevance</t>
         </is>
       </c>
-      <c r="D12" s="12" t="n">
+      <c r="D19" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="E19" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="F12" s="13" t="n">
+      <c r="F19" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>No resume evidence of the industry/domain the JD asks for: Preferred: experience in edtech or another high-consideration B2C c....</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>No direct quote available for this category.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Candidate 007</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Candidate 008</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>unnamed_candidate_resume.docx</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Education &amp; Certifications</t>
         </is>
       </c>
-      <c r="D13" s="12" t="n">
+      <c r="D20" s="12" t="n">
         <v>8.1</v>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="E20" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="F13" s="13" t="n">
+      <c r="F20" s="13" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>Matched 2 of 2 education/certification requirement(s).</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>• "Bachelor of Business Administration, 2015"
 • "Ran paid search and paid social for an edtech platform selling professional certification courses."</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Candidate 007</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Candidate 008</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>unnamed_candidate_resume.docx</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>Preferred Requirements</t>
         </is>
       </c>
-      <c r="D14" s="12" t="n">
+      <c r="D21" s="12" t="n">
         <v>3.5</v>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="E21" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="F14" s="13" t="n">
+      <c r="F21" s="13" t="n">
         <v>0.35</v>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>Evidenced 4 of 11 preferred requirement(s).</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>• "Owned paid media across Google Ads, Meta Ads and programmatic display."
 • "Used GA4 and SQL for funnel analysis and cohort reporting."
@@ -2097,32 +2478,32 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>Candidate 007</t>
-        </is>
-      </c>
-      <c r="B15" s="14" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>Candidate 008</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>unnamed_candidate_resume.docx</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C22" s="14" t="inlineStr">
         <is>
           <t>Mandatory Requirements</t>
         </is>
       </c>
-      <c r="D15" s="14" t="n">
+      <c r="D22" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="E15" s="14" t="n">
+      <c r="E22" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="F15" s="15" t="n">
+      <c r="F22" s="15" t="n">
         <v>0.8571</v>
       </c>
-      <c r="G15" s="14" t="inlineStr">
+      <c r="G22" s="14" t="inlineStr">
         <is>
           <t>Met: • Must have 5+ years of hands-on performance marketing experience.
 • Required: proven expertise running Google Ads and Meta Ads at scale.
@@ -2133,84 +2514,84 @@
 Missed: • This is a hybrid role based in Bengaluru. Candidates must be willing to work from the Bengaluru office three days a week.</t>
         </is>
       </c>
-      <c r="H15" s="14" t="inlineStr">
+      <c r="H22" s="14" t="inlineStr">
         <is>
           <t>• "[Mandatory: strong command of conversion rate optimization...] Led conversion rate optimization and a continuous A/B testing programme on landing pages."
 • "[Nice to have: exposure to lifecycle and email marketing.] Google Ads, Meta Ads, GA4, SQL, CRO, A/B testing, programmatic, lifecycle marketing"
 • "[Advantage: Google Ads certification.] Ran paid search and paid social for an edtech platform selling professional certification courses."
 • "[Required: proven expertise running Google Ads and Meta Ad...] Owned paid media across Google Ads, Meta Ads and programmatic display."
 • "[Essential: working knowledge of GA4 and marketing analyti...] Used GA4 and SQL for funnel analysis and cohort reporting."
-• "[Must have 5+ years of hands-on performance marketing expe...] Growth marketing lead with 8 years of experience in paid acquisition for"</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+• "[Must have 5+ years of hands-on performance marketing expe...] Growth marketing lead with 8 years of experience in paid acquisition for consumer subscription businesses."</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Rahul Nair</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>rahul_nair_resume.docx</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>Relevant Experience</t>
         </is>
       </c>
-      <c r="D16" s="12" t="n">
+      <c r="D23" s="12" t="n">
         <v>6.7</v>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="E23" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="F16" s="13" t="n">
+      <c r="F23" s="13" t="n">
         <v>0.268</v>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>Role relevance 12%, title relevance 0%, duration fit 80%. Most relevant title held: Digital Marketing Specialist 4 years of experience (stated in resume) is below the JD minimum of 5.</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>• "Managed paid acquisition for enterprise SaaS products across search and social."</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>Rahul Nair</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>rahul_nair_resume.docx</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>Required Skills</t>
         </is>
       </c>
-      <c r="D17" s="12" t="n">
+      <c r="D24" s="12" t="n">
         <v>11.9</v>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="E24" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="F17" s="13" t="n">
+      <c r="F24" s="13" t="n">
         <v>0.476</v>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>Evidenced 3 of 5 required skill/experience requirement(s). Not evidenced: Required: proven expertise running Google Ads and Meta Ads at scale.; Mandatory: strong command of conversion rate optimization and A/B t....</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>• "Managed paid acquisition for enterprise SaaS products across search and social."
 • "Google Ads, LinkedIn Ads, SEO, HubSpot, email marketing, Google Analytics"
@@ -2218,178 +2599,178 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>Rahul Nair</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>rahul_nair_resume.docx</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>JD Alignment</t>
         </is>
       </c>
-      <c r="D18" s="12" t="n">
+      <c r="D25" s="12" t="n">
         <v>3.2</v>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="E25" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="F18" s="13" t="n">
+      <c r="F25" s="13" t="n">
         <v>0.16</v>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>Overall requirement coverage 27%; evidence aligns with 0 of 6 key responsibilities in the JD.</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>No direct quote available for this category.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>Rahul Nair</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>rahul_nair_resume.docx</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>Industry / Domain Relevance</t>
         </is>
       </c>
-      <c r="D19" s="12" t="n">
+      <c r="D26" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="E26" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="F19" s="13" t="n">
+      <c r="F26" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>No resume evidence of the industry/domain the JD asks for: Preferred: experience in edtech or another high-consideration B2C c....</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>No direct quote available for this category.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>Rahul Nair</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>rahul_nair_resume.docx</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>Education &amp; Certifications</t>
         </is>
       </c>
-      <c r="D20" s="12" t="n">
+      <c r="D27" s="12" t="n">
         <v>7.3</v>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="E27" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="F20" s="13" t="n">
+      <c r="F27" s="13" t="n">
         <v>0.73</v>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>Matched 2 of 2 education/certification requirement(s).</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>• "B.Tech, Computer Science - Pune Institute of Technology, 2020"
 • "Grew inbound demo requests 60% year on year through paid search and content."</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>Rahul Nair</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>rahul_nair_resume.docx</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>Preferred Requirements</t>
         </is>
       </c>
-      <c r="D21" s="12" t="n">
+      <c r="D28" s="12" t="n">
         <v>1.6</v>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="E28" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="F21" s="13" t="n">
+      <c r="F28" s="13" t="n">
         <v>0.16</v>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>Evidenced 2 of 11 preferred requirement(s).</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t>• "Supported SEO and email marketing campaigns."
 • "Grew inbound demo requests 60% year on year through paid search and content."</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
         <is>
           <t>Rahul Nair</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>rahul_nair_resume.docx</t>
         </is>
       </c>
-      <c r="C22" s="14" t="inlineStr">
+      <c r="C29" s="14" t="inlineStr">
         <is>
           <t>Mandatory Requirements</t>
         </is>
       </c>
-      <c r="D22" s="14" t="n">
+      <c r="D29" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="E22" s="14" t="n">
+      <c r="E29" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="F22" s="15" t="n">
+      <c r="F29" s="15" t="n">
         <v>0.5714</v>
       </c>
-      <c r="G22" s="14" t="inlineStr">
+      <c r="G29" s="14" t="inlineStr">
         <is>
           <t>Met: • Must have 5+ years of hands-on performance marketing experience.
 • Essential: working knowledge of GA4 and marketing analytics dashboards.
@@ -2400,7 +2781,7 @@
 • This is a hybrid role based in Bengaluru. Candidates must be willing to work from the Bengaluru office three days a week.</t>
         </is>
       </c>
-      <c r="H22" s="14" t="inlineStr">
+      <c r="H29" s="14" t="inlineStr">
         <is>
           <t>• "[Nice to have: exposure to lifecycle and email marketing.] Supported SEO and email marketing campaigns."
 • "[Advantage: Google Ads certification.] Grew inbound demo requests 60% year on year through paid search and content."
@@ -2411,248 +2792,248 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>Vikram Desai</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>vikram_desai_resume.pdf</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>Relevant Experience</t>
         </is>
       </c>
-      <c r="D23" s="12" t="n">
+      <c r="D30" s="12" t="n">
         <v>7.1</v>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="E30" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="F23" s="13" t="n">
+      <c r="F30" s="13" t="n">
         <v>0.284</v>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="G30" s="3" t="inlineStr">
         <is>
           <t>Role relevance 0%, title relevance 17%, duration fit 100%. Most relevant title held: Senior Software Engineer 6 years of experience (stated in resume) meets the JD minimum of 5.</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="H30" s="3" t="inlineStr">
         <is>
           <t>No direct quote available for this category.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>Vikram Desai</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>vikram_desai_resume.pdf</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>Required Skills</t>
         </is>
       </c>
-      <c r="D24" s="12" t="n">
+      <c r="D31" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="E31" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="F24" s="13" t="n">
+      <c r="F31" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>Evidenced 0 of 5 required skill/experience requirement(s). Not evidenced: Must have 5+ years of hands-on performance marketing experience.; Required: proven expertise running Google Ads and Meta Ads at scale.; Mandatory: strong command of conversion rate optimization and A/B t...; Essential: working knowledge of GA4 and marketing analytics dashboa...; Must have experience owning CAC, ROAS and unit economics for a paid....</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>No direct quote available for this category.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>Vikram Desai</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>vikram_desai_resume.pdf</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>JD Alignment</t>
         </is>
       </c>
-      <c r="D25" s="12" t="n">
+      <c r="D32" s="12" t="n">
         <v>0.8</v>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="E32" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="F25" s="13" t="n">
+      <c r="F32" s="13" t="n">
         <v>0.04</v>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="G32" s="3" t="inlineStr">
         <is>
           <t>Overall requirement coverage 6%; evidence aligns with 0 of 6 key responsibilities in the JD.</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="H32" s="3" t="inlineStr">
         <is>
           <t>No direct quote available for this category.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>Vikram Desai</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>vikram_desai_resume.pdf</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>Industry / Domain Relevance</t>
         </is>
       </c>
-      <c r="D26" s="12" t="n">
+      <c r="D33" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="E33" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="F26" s="13" t="n">
+      <c r="F33" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>No resume evidence of the industry/domain the JD asks for: Preferred: experience in edtech or another high-consideration B2C c....</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>No direct quote available for this category.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>Vikram Desai</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>vikram_desai_resume.pdf</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>Education &amp; Certifications</t>
         </is>
       </c>
-      <c r="D27" s="12" t="n">
+      <c r="D34" s="12" t="n">
         <v>3.3</v>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="E34" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="F27" s="13" t="n">
+      <c r="F34" s="13" t="n">
         <v>0.33</v>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="G34" s="3" t="inlineStr">
         <is>
           <t>Matched 1 of 2 education/certification requirement(s). Not evidenced: Advantage: Google Ads certification..</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="H34" s="3" t="inlineStr">
         <is>
           <t>• "B.Tech, Information Technology - NIT Warangal, 2018"</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>Vikram Desai</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>vikram_desai_resume.pdf</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>Preferred Requirements</t>
         </is>
       </c>
-      <c r="D28" s="12" t="n">
+      <c r="D35" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="E35" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="F28" s="13" t="n">
+      <c r="F35" s="13" t="n">
         <v>0.05</v>
       </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr">
         <is>
           <t>Evidenced 0 of 11 preferred requirement(s).</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr">
         <is>
           <t>No direct quote available for this category.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="14" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="14" t="inlineStr">
         <is>
           <t>Vikram Desai</t>
         </is>
       </c>
-      <c r="B29" s="14" t="inlineStr">
+      <c r="B36" s="14" t="inlineStr">
         <is>
           <t>vikram_desai_resume.pdf</t>
         </is>
       </c>
-      <c r="C29" s="14" t="inlineStr">
+      <c r="C36" s="14" t="inlineStr">
         <is>
           <t>Mandatory Requirements</t>
         </is>
       </c>
-      <c r="D29" s="14" t="n">
+      <c r="D36" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="E29" s="14" t="n">
+      <c r="E36" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="F29" s="15" t="n">
+      <c r="F36" s="15" t="n">
         <v>0.1429</v>
       </c>
-      <c r="G29" s="14" t="inlineStr">
+      <c r="G36" s="14" t="inlineStr">
         <is>
           <t>Met: • Required qualification: Bachelor's degree in any discipline.
 Missed: • Must have 5+ years of hands-on performance marketing experience.
@@ -2663,7 +3044,7 @@
 • This is a hybrid role based in Bengaluru. Candidates must be willing to work from the Bengaluru office three days a week.</t>
         </is>
       </c>
-      <c r="H29" s="14" t="inlineStr">
+      <c r="H36" s="14" t="inlineStr">
         <is>
           <t>• "[Required qualification: Bachelor's degree in any discipline.] B.Tech, Information Technology - NIT Warangal, 2018"
 • "[Good to have: experience with SQL for self-serve funnel a...] Python, Go, Kubernetes, Docker, PostgreSQL, AWS, REST APIs, CI/CD"
@@ -2671,113 +3052,113 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>Anjali Mehta</t>
         </is>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B37" s="9" t="inlineStr">
         <is>
           <t>anjali_mehta_resume_copy.docx</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C37" s="9" t="inlineStr">
         <is>
           <t>Not evaluated</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr"/>
-      <c r="E30" s="9" t="inlineStr"/>
-      <c r="F30" s="9" t="inlineStr"/>
-      <c r="G30" s="9" t="inlineStr">
+      <c r="D37" s="9" t="inlineStr"/>
+      <c r="E37" s="9" t="inlineStr"/>
+      <c r="F37" s="9" t="inlineStr"/>
+      <c r="G37" s="9" t="inlineStr">
         <is>
           <t>Duplicate of 'anjali_mehta_resume.pdf' — not analysed again. See the original entry for the evaluation.</t>
         </is>
       </c>
-      <c r="H30" s="9" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="H37" s="9" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>Candidate 003</t>
         </is>
       </c>
-      <c r="B31" s="9" t="inlineStr">
+      <c r="B38" s="9" t="inlineStr">
         <is>
           <t>corrupted_resume.pdf</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
+      <c r="C38" s="9" t="inlineStr">
         <is>
           <t>Not evaluated</t>
         </is>
       </c>
-      <c r="D31" s="9" t="inlineStr"/>
-      <c r="E31" s="9" t="inlineStr"/>
-      <c r="F31" s="9" t="inlineStr"/>
-      <c r="G31" s="9" t="inlineStr">
+      <c r="D38" s="9" t="inlineStr"/>
+      <c r="E38" s="9" t="inlineStr"/>
+      <c r="F38" s="9" t="inlineStr"/>
+      <c r="G38" s="9" t="inlineStr">
         <is>
           <t>Corrupted or unreadable PDF (No /Root object! - Is this really a PDF?).</t>
         </is>
       </c>
-      <c r="H31" s="9" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="H38" s="9" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>Candidate 004</t>
         </is>
       </c>
-      <c r="B32" s="9" t="inlineStr">
+      <c r="B39" s="9" t="inlineStr">
         <is>
           <t>empty_resume.txt</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
+      <c r="C39" s="9" t="inlineStr">
         <is>
           <t>Not evaluated</t>
         </is>
       </c>
-      <c r="D32" s="9" t="inlineStr"/>
-      <c r="E32" s="9" t="inlineStr"/>
-      <c r="F32" s="9" t="inlineStr"/>
-      <c r="G32" s="9" t="inlineStr">
+      <c r="D39" s="9" t="inlineStr"/>
+      <c r="E39" s="9" t="inlineStr"/>
+      <c r="F39" s="9" t="inlineStr"/>
+      <c r="G39" s="9" t="inlineStr">
         <is>
           <t>Empty file (0 bytes).</t>
         </is>
       </c>
-      <c r="H32" s="9" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="H39" s="9" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
         <is>
           <t>Candidate 005</t>
         </is>
       </c>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="B40" s="9" t="inlineStr">
         <is>
           <t>meera_iyer_resume.txt</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C40" s="9" t="inlineStr">
         <is>
           <t>Not evaluated</t>
         </is>
       </c>
-      <c r="D33" s="9" t="inlineStr"/>
-      <c r="E33" s="9" t="inlineStr"/>
-      <c r="F33" s="9" t="inlineStr"/>
-      <c r="G33" s="9" t="inlineStr">
+      <c r="D40" s="9" t="inlineStr"/>
+      <c r="E40" s="9" t="inlineStr"/>
+      <c r="F40" s="9" t="inlineStr"/>
+      <c r="G40" s="9" t="inlineStr">
         <is>
           <t>Empty resume — no usable text could be extracted.</t>
         </is>
       </c>
-      <c r="H33" s="9" t="inlineStr"/>
+      <c r="H40" s="9" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H33"/>
-  <conditionalFormatting sqref="F2:F33">
+  <autoFilter ref="A1:H40"/>
+  <conditionalFormatting sqref="F2:F40">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -2799,7 +3180,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2819,7 +3200,7 @@
     <row r="2">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Generated 19 Sep 2026, 10:27  ·  Analysis: Offline heuristic analyzer</t>
+          <t>Generated 19 Sep 2026, 11:06  ·  Analysis: Offline heuristic analyzer</t>
         </is>
       </c>
     </row>
@@ -2900,7 +3281,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -2910,7 +3291,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -2967,7 +3348,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -3004,7 +3385,7 @@
         </is>
       </c>
       <c r="B25" s="25" t="n">
-        <v>44.3</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="26">
@@ -3177,11 +3558,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Candidate 007</t>
+          <t>Priya Raghavan</t>
         </is>
       </c>
       <c r="C42" s="28" t="n">
-        <v>54.2</v>
+        <v>59</v>
       </c>
       <c r="D42" s="30" t="inlineStr">
         <is>
@@ -3190,7 +3571,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>unnamed_candidate_resume.docx</t>
+          <t>scanned_resume.pdf</t>
         </is>
       </c>
     </row>
@@ -3200,20 +3581,20 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Rahul Nair</t>
+          <t>Candidate 008</t>
         </is>
       </c>
       <c r="C43" s="28" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="D43" s="31" t="inlineStr">
-        <is>
-          <t>Weak Match</t>
+        <v>54.2</v>
+      </c>
+      <c r="D43" s="30" t="inlineStr">
+        <is>
+          <t>Partial Match</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>rahul_nair_resume.docx</t>
+          <t>unnamed_candidate_resume.docx</t>
         </is>
       </c>
     </row>
@@ -3223,25 +3604,48 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
+          <t>Rahul Nair</t>
+        </is>
+      </c>
+      <c r="C44" s="28" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="D44" s="31" t="inlineStr">
+        <is>
+          <t>Weak Match</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>rahul_nair_resume.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
           <t>Vikram Desai</t>
         </is>
       </c>
-      <c r="C44" s="28" t="n">
+      <c r="C45" s="28" t="n">
         <v>11.7</v>
       </c>
-      <c r="D44" s="31" t="inlineStr">
+      <c r="D45" s="31" t="inlineStr">
         <is>
           <t>Weak Match</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>vikram_desai_resume.pdf</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="17" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="17" t="inlineStr">
         <is>
           <t>Scores are evidence-based: see the 'Detailed Evaluation' sheet for the reasoning and the resume quote behind every category score.</t>
         </is>

--- a/outputs/sample_candidate_ranking.xlsx
+++ b/outputs/sample_candidate_ranking.xlsx
@@ -3200,7 +3200,7 @@
     <row r="2">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Generated 19 Sep 2026, 11:06  ·  Analysis: Offline heuristic analyzer</t>
+          <t>Generated 19 Sep 2026, 12:33  ·  Analysis: Offline heuristic analyzer</t>
         </is>
       </c>
     </row>
